--- a/data/trans_dic/IP31KM13_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM13_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,11; 98,77</t>
+          <t>68,67; 97,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,11; 96,56</t>
+          <t>92,12; 98,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,25; 96,78</t>
+          <t>83,44; 96,91</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,27; 96,61</t>
+          <t>90,22; 96,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,15; 96,14</t>
+          <t>90,04; 96,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,53; 95,92</t>
+          <t>91,03; 95,72</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,27; 92,24</t>
+          <t>77,61; 89,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,01; 89,92</t>
+          <t>78,8; 89,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,2; 89,74</t>
+          <t>80,34; 87,88</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,6; 96,47</t>
+          <t>92,35; 98,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,23; 98,52</t>
+          <t>89,72; 96,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,68; 96,75</t>
+          <t>92,31; 96,69</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,8; 93,96</t>
+          <t>86,75; 93,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,79; 93,42</t>
+          <t>90,18; 93,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,21; 93,17</t>
+          <t>89,57; 93,07</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>182</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>110337</t>
+          <t>109690</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>120592</t>
+          <t>114656</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>230929</t>
+          <t>224347</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>106381; 112843</t>
+          <t>84390; 119351</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87709; 132114</t>
+          <t>109250; 116944</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>193956; 242990</t>
+          <t>201513; 234038</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>254</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>175811</t>
+          <t>216552</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>231981</t>
+          <t>169778</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407792</t>
+          <t>386329</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>168000; 179805</t>
+          <t>208620; 222627</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>223149; 237971</t>
+          <t>162604; 174444</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>396925; 415924</t>
+          <t>374909; 394215</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>189</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>162634</t>
+          <t>139746</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>155693</t>
+          <t>131567</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318328</t>
+          <t>271312</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>151099; 173637</t>
+          <t>129229; 148207</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>146482; 164626</t>
+          <t>122173; 137981</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301513; 333255</t>
+          <t>258345; 282573</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>221</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>154370</t>
+          <t>160023</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>170927</t>
+          <t>153802</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325297</t>
+          <t>313825</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>147416; 158720</t>
+          <t>153456; 163362</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165304; 174693</t>
+          <t>147116; 157888</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>316797; 330704</t>
+          <t>304769; 319227</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>846</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>603153</t>
+          <t>626011</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>679193</t>
+          <t>569803</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1282346</t>
+          <t>1195814</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>586492; 613665</t>
+          <t>595829; 640733</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>638897; 695737</t>
+          <t>557527; 579751</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1247065; 1302456</t>
+          <t>1168873; 1214604</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM13_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM13_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan lácteos (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>89,25%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>68,67; 97,12</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>92,12; 98,61</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>83,44; 96,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>94,01%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>90,22; 96,27</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>90,04; 96,6</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>91,03; 95,72</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>83,92%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>84,37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>77,61; 89,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>78,8; 89,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>80,34; 87,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>93,79%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>95,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>92,35; 98,31</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>89,72; 96,29</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>92,31; 96,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>91,15%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>86,75; 93,29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>90,18; 93,78</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>89,57; 93,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8925462910514047</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9667638658954338</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9289945310442153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>109690</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>114656</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>224347</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.6866746485962929</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9211831448256936</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8344445345974028</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>84390; 119351</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>109250; 116944</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>201513; 234038</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9711506847626331</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9860532690192805</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.969126259824429</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9364779080703404</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9401153406220231</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9380729565997351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>216552</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>169778</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>386329</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9021770671514133</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9003914066582636</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.910343455324011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>208620; 222627</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>162604; 174444</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>374909; 394215</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9627484169736786</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9659509015294735</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9572194474949778</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.8392039672452939</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8486083916297217</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8437382529508651</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>139746</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>131567</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>271312</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7760501895059828</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7880170897513522</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8034110839506364</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>129229; 148207</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>122173; 137981</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>258345; 282573</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8900122917687386</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.8899796534542914</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8787569630366696</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9630365667864501</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9379389169502806</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9505708311256386</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>160023</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>153802</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>313825</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9235138205883803</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8971606274301475</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9231407530676855</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>153456; 163362</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>147116; 157888</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>304769; 319227</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.983133436882636</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9628553742697885</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9669314148732145</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1715</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9114581644351256</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9217016123661534</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9163105981526873</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>626011</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>569803</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1195814</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8675134355668738</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.901844322994351</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8956665053641897</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>595829; 640733</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>557527; 579751</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1168873; 1214604</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9328919465149366</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9377933183047676</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9307088302404574</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan lácteos (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>109690</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>114656</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>224347</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>84390</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>109250</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>201513</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>119351</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>116944</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>234038</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>304</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>254</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>216552</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>169778</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>386329</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>208620</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>162604</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>374909</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>222627</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>174444</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>394215</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>139746</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>131567</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>271312</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>129229</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>122173</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>258345</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>148207</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>137981</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>282573</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>224</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>221</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>160023</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>153802</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>313825</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>153456</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>147116</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>304769</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>163362</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>157888</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>319227</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>869</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>846</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>626011</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>569803</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1195814</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>595829</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>557527</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1168873</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>640733</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>579751</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1214604</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>